--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260729.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260729.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>153,285</t>
+          <t>152,735</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>28.71%</t>
+          <t>28.56%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>17,415</t>
+          <t>17,315</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.87%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>110,850</t>
+          <t>110,550</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.54%</t>
+          <t>6.58%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>135,195</t>
+          <t>134,845</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.94%</t>
+          <t>6.03%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>56,475</t>
+          <t>56,295</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.85%</t>
+          <t>4.65%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>66,320</t>
+          <t>66,220</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>3.87%</t>
         </is>
       </c>
     </row>
@@ -743,56 +743,56 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>73,105</t>
+          <t>73,005</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.54%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>6,325</t>
+          <t>50,435</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.29%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>50,435</t>
+          <t>6,325</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>85,615</t>
+          <t>85,365</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -946,73 +946,73 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>21,690</t>
+          <t>40,290</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>40,290</t>
+          <t>66,058</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>66,158</t>
+          <t>21,690</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -1029,166 +1029,166 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>23,798</t>
+          <t>23,698</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,514,827</t>
+          <t>141,205</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>141,205</t>
+          <t>20,515</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>20,515</t>
+          <t>8,790</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>8,790</t>
+          <t>66,944,471</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>12,951</t>
+          <t>17,671</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>10,666</t>
+          <t>12,951</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>17,671</t>
+          <t>10,566</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>49,876,688</t>
+          <t>1,514,827</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>21,787</t>
+          <t>21,687</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -1315,10 +1315,32 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>32,238,000</t>
+          <t>32,377,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>RDI_USD</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>466,876</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
